--- a/example_run/final_quote.xlsx
+++ b/example_run/final_quote.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,15 +490,25 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>Contact Type</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Contact / Link</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Status Detail</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Evaluation Record Reference</t>
         </is>
@@ -545,15 +555,25 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>quotes@mcmaster-example.com</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>SUBSTITUTION</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Quote is for an equivalent part, not an exact match to the BOM line - needs engineering sign-off. Price not yet received.</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>comparison_bom.xlsx, Source Row 4</t>
         </is>
@@ -600,15 +620,25 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>sales@fastenco-example.com</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>SUBSTITUTION</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Quote is for an equivalent part, not an exact match to the BOM line - needs engineering sign-off. Price not yet received.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>comparison_bom.xlsx, Source Row 5</t>
         </is>
@@ -655,15 +685,25 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>sales@andymark-example.com</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>SUBSTITUTION</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Quote is for an equivalent part, not an exact match to the BOM line - needs engineering sign-off. Price not yet received.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>comparison_bom.xlsx, Source Row 6</t>
         </is>
@@ -701,19 +741,34 @@
           <t>ElectroConn</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>UNSOURCED</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A likely part/manufacturer match exists, but no contact method or portal login has been established for this supplier - unexplored source, needs manual outreach before it can be qualified or quoted.</t>
+          <t>https://www.electroconn-example.com/products/TB-100</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
+        <is>
+          <t>SUBSTITUTION</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Quote is for an equivalent part, not an exact match to the BOM line - needs engineering sign-off. Price not yet received.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>comparison_bom.xlsx, Source Row 7</t>
         </is>
@@ -765,15 +820,25 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
+          <t>PORTAL</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>https://portal.linearmotion-example.com/rfq</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>SUBSTITUTION</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Quote is for an equivalent part, not an exact match to the BOM line - needs engineering sign-off. Price not yet received.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>comparison_bom.xlsx, Source Row 8</t>
         </is>
@@ -811,19 +876,34 @@
           <t>MeanTech</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>UNSOURCED</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A likely part/manufacturer match exists, but no contact method or portal login has been established for this supplier - unexplored source, needs manual outreach before it can be qualified or quoted.</t>
+          <t>https://www.meantech-example.com/shop/PSU-24-5A</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
+        <is>
+          <t>SUBSTITUTION</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Quote is for an equivalent part, not an exact match to the BOM line - needs engineering sign-off. Price not yet received.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>comparison_bom.xlsx, Source Row 9</t>
         </is>
@@ -855,15 +935,21 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>UNSOURCED</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>No supplier could be identified for this line.</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>comparison_bom.xlsx, Source Row 10</t>
         </is>
@@ -880,7 +966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,7 +1107,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>No saved email contact or portal login for 'ElectroConn' - this source hasn't been explored yet. Needs manual outreach before qualification or an RFQ can proceed.</t>
+          <t>'ElectroConn' is not yet an approved vendor (ISO 9001 status: Unknown) - needs qualification review before an RFQ can be sent.</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1117,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>No saved email contact or portal login for 'MeanTech' - this source hasn't been explored yet. Needs manual outreach before qualification or an RFQ can proceed.</t>
+          <t>'MeanTech' is not yet an approved vendor (ISO 9001 status: Unknown) - needs qualification review before an RFQ can be sent.</t>
         </is>
       </c>
     </row>
@@ -1077,29 +1163,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Email content received for RESIN8-RFQ-0004 but quote fields could not be extracted (no LLM access) - needs manual read: Thanks for reaching out. For part 1234K56 (Aluminum mounting bracket for NEMA 17 servo motors), qty 4: unit price $8.75, extended price $35.00. In stock, ships in 2 business days. Quote valid 30 days </t>
+          <t>Distributor part - pricing should come from a Stage 2 catalog query, not an RFQ. Skipped here.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Email content received for RESIN8-RFQ-0006 but quote fields could not be extracted (no LLM access) - needs manual read: We can supply the am-3103a gearbox. Note: minimum order quantity is 5 units, your request was for 2 - happy to quote at 5 if that works. Unit price at MOQ $42.00, extended $210.00. Lead time 3 weeks, </t>
+          <t>Distributor part - pricing should come from a Stage 2 catalog query, not an RFQ. Skipped here.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Email content received for RESIN8-RFQ-0004 but quote fields could not be extracted (no LLM access) - needs manual read: Thanks for reaching out. For part 1234K56 (Aluminum mounting bracket for NEMA 17 servo motors), qty 4: unit price $8.75, extended price $35.00. In stock, ships in 2 business days. Quote valid 30 days </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Email content received for RESIN8-RFQ-0006 but quote fields could not be extracted (no LLM access) - needs manual read: We can supply the am-3103a gearbox. Note: minimum order quantity is 5 units, your request was for 2 - happy to quote at 5 if that works. Unit price at MOQ $42.00, extended $210.00. Lead time 3 weeks, </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
         <v>8</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Portal content received for 8 but quote fields could not be extracted (no LLM access) - needs manual read: My Account &gt; Quotes
 Quote #Q-88213 - LM6UU Linear ball bearing, 6mm bore
@@ -1109,31 +1215,31 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Only one candidate quote available for this line - nothing to compare against yet (see Stage 2/3 known limitation).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>6</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Only one candidate quote available for this line - nothing to compare against yet (see Stage 2/3 known limitation).</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Only one candidate quote available for this line - nothing to compare against yet (see Stage 2/3 known limitation).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Only one candidate quote available for this line - nothing to compare against yet (see Stage 2/3 known limitation).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>8</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Only one candidate quote available for this line - nothing to compare against yet (see Stage 2/3 known limitation).</t>
         </is>
